--- a/.storybook/public/audit_ecoconception_dev_front.xlsx
+++ b/.storybook/public/audit_ecoconception_dev_front.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHINKARETZKY-32281\Desktop\Eco Conception\1. Focus UX UI Dev Front\Audit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F8E7EE8-CF97-4B03-B437-2317D072D925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7BCCD2-363F-442D-9DE2-50EADA1863F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info Projet" sheetId="1" r:id="rId1"/>
@@ -273,75 +273,6 @@
     <t>Exigences Non Fonctionnelles</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Objectif de l'échantillonage</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-L'objectif de l'échantillonage est de lister les pages du produit à auditer pour l'Eco-Conception (entre 10 et 15 pages). 
-Utilisez l</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>e tableau de la feuille "Echantillonage" Ligne 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> pour lister l'ensemble des pages du produit que vous avez identifiées comme pertinentes à auditer.
-Une fois que vous aurez sélectionné les pages, vous n'aurez qu'à</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> dupliquer la feuille " Flash P1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">" autant de fois que le nombre de pages à auditer.
-</t>
-    </r>
-  </si>
-  <si>
     <t>Ouvrir le document des 20 bonnes pratiques essentielles écoconception</t>
   </si>
   <si>
@@ -526,6 +457,75 @@
         <family val="2"/>
       </rPr>
       <t>".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Objectif de l'échantillonage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+L'objectif de l'échantillonage est de lister les pages du produit à évaluer pour l'écoconception (entre 10 et 15 pages). 
+Utilisez l</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>e tableau de la feuille "Echantillonage" Ligne 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pour lister l'ensemble des pages du produit que vous avez identifiées comme pertinentes à auditer.
+Une fois que vous aurez sélectionné les pages, vous n'aurez qu'à</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dupliquer la feuille " Page1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" autant de fois que le nombre de pages à évaluer.
+</t>
     </r>
   </si>
 </sst>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="2" spans="1:4" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="38" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -1740,7 +1740,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="10" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="17" t="s">
@@ -1776,11 +1776,11 @@
     </row>
     <row r="4" spans="1:8" s="10" customFormat="1" ht="53.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" s="21"/>
       <c r="C4" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1796,7 +1796,7 @@
     </row>
     <row r="6" spans="1:8" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
@@ -1814,7 +1814,7 @@
     </row>
     <row r="8" spans="1:8" s="10" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B8" s="41"/>
       <c r="C8" s="41"/>
@@ -1836,13 +1836,13 @@
         <v>31</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" s="25" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>2</v>
@@ -1856,13 +1856,13 @@
         <v>29</v>
       </c>
       <c r="B11" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="27" t="s">
-        <v>46</v>
-      </c>
       <c r="D11" s="28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" s="29" t="s">
         <v>4</v>
@@ -1873,13 +1873,13 @@
     <row r="12" spans="1:8" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="45"/>
       <c r="B12" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" s="29" t="s">
         <v>3</v>
@@ -1890,13 +1890,13 @@
     <row r="13" spans="1:8" ht="52.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="46"/>
       <c r="B13" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" s="29" t="s">
         <v>3</v>
@@ -1906,16 +1906,16 @@
     </row>
     <row r="14" spans="1:8" s="10" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="28" t="s">
         <v>37</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>38</v>
       </c>
       <c r="E14" s="29" t="s">
         <v>3</v>
@@ -1926,13 +1926,13 @@
     <row r="15" spans="1:8" s="10" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="43"/>
       <c r="B15" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E15" s="29" t="s">
         <v>3</v>
@@ -1945,13 +1945,13 @@
         <v>27</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" s="29" t="s">
         <v>3</v>
@@ -1962,13 +1962,13 @@
     <row r="17" spans="1:8" s="10" customFormat="1" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48"/>
       <c r="B17" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="27" t="s">
-        <v>58</v>
-      </c>
       <c r="D17" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E17" s="29" t="s">
         <v>3</v>
@@ -1979,13 +1979,13 @@
     <row r="18" spans="1:8" s="10" customFormat="1" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="48"/>
       <c r="B18" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="27" t="s">
-        <v>60</v>
-      </c>
       <c r="D18" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E18" s="29" t="s">
         <v>3</v>
@@ -1996,13 +1996,13 @@
     <row r="19" spans="1:8" s="10" customFormat="1" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="49"/>
       <c r="B19" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="27" t="s">
-        <v>62</v>
-      </c>
       <c r="D19" s="28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E19" s="29" t="s">
         <v>3</v>
@@ -2015,10 +2015,10 @@
         <v>28</v>
       </c>
       <c r="B20" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="27" t="s">
         <v>63</v>
-      </c>
-      <c r="C20" s="27" t="s">
-        <v>64</v>
       </c>
       <c r="D20" s="28"/>
       <c r="E20" s="29" t="s">
